--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -760,7 +760,7 @@
         <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -790,7 +790,7 @@
         <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.86</v>
       </c>
       <c r="G5" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
         <v>2.24</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
         <v>4.9</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>3.75</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="H12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="H13" t="n">
         <v>2.06</v>
@@ -2903,7 +2903,7 @@
         <v>2.32</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 00:47:57</t>
+          <t>2026-05-06 02:59:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -760,7 +760,7 @@
         <v>1.82</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -772,7 +772,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.96</v>
       </c>
       <c r="G3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
         <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G5" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.02</v>
       </c>
       <c r="G8" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="H10" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>2.92</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="K11" t="n">
         <v>3.05</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
         <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>3.05</v>
       </c>
       <c r="G13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H13" t="n">
         <v>2.06</v>
@@ -2903,7 +2903,7 @@
         <v>2.32</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="H14" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 02:59:05</t>
+          <t>2026-05-06 05:09:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH14"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Indian Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hyderabad FC</t>
+          <t>Kryvbas Krivyi Rih</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.82</v>
+        <v>2.86</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>2.58</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Indian Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hyderabad FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.96</v>
+        <v>1.82</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>3.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>3.55</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
-        <v>2.54</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.92</v>
+        <v>5.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Polissya Zhytomyr</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Digenis Ypsona</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>1.21</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>1.3</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Digenis Ypsona</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.2</v>
       </c>
-      <c r="G10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.9</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J12" t="n">
         <v>2.9</v>
       </c>
-      <c r="G12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.68</v>
-      </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,32 +2882,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.05</v>
       </c>
-      <c r="G13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.82</v>
+        <v>1.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.46</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,201 +3054,589 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 05:09:58</t>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pharco FC</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-05-06 07:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-05-06 07:21:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>South African Premier Division</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>14:30:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Durban City</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Stellenbosch FC</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F16" t="n">
         <v>2.86</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G16" t="n">
         <v>3.55</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" t="n">
         <v>2.92</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" t="n">
         <v>3.7</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>2.6</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K16" t="n">
         <v>3.1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q16" t="n">
         <v>3.05</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>2026-05-06 05:09:58</t>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-05-06 07:21:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="G2" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
@@ -778,133 +778,133 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>1.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="S2" t="n">
         <v>2.68</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
         <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
         <v>1.01</v>
@@ -913,14 +913,14 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>5.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
         <v>3.15</v>
@@ -1372,7 +1372,7 @@
         <v>1.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.84</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
         <v>2.54</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Polissya Zhytomyr</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Polissya Zhytomyr</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Digenis Ypsona</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Digenis Ypsona</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>3.05</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>2.9</v>
       </c>
-      <c r="G14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.68</v>
-      </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>2.96</v>
       </c>
       <c r="I15" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>2.7</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.8</v>
+        <v>1.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,201 +3442,589 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 07:21:25</t>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pharco FC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>South African Premier Division</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>14:30:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Durban City</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Stellenbosch FC</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
         <v>2.86</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G18" t="n">
         <v>3.55</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H18" t="n">
         <v>2.92</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I18" t="n">
         <v>3.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J18" t="n">
         <v>2.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K18" t="n">
         <v>3.1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q18" t="n">
         <v>3.05</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-05-06 07:21:25</t>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:33:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -775,7 +775,7 @@
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -784,7 +784,7 @@
         <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
         <v>2.2</v>
@@ -799,49 +799,49 @@
         <v>2.68</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG2" t="n">
         <v>14</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AH2" t="n">
         <v>18</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
         <v>34</v>
@@ -850,31 +850,31 @@
         <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO2" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
         <v>11.5</v>
@@ -883,19 +883,19 @@
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BG2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
@@ -951,112 +951,112 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.24</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP3" t="n">
         <v>1.03</v>
@@ -1071,34 +1071,34 @@
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AY3" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
         <v>1.03</v>
@@ -1107,21 +1107,21 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Imisli FK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.68</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
@@ -1330,186 +1330,186 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.96</v>
       </c>
       <c r="G5" t="n">
-        <v>2.36</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="I5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU5" t="n">
         <v>5.3</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>2.54</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.18</v>
-      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>2.92</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,17 +1907,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Olympique Akbou</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1936,7 +1936,7 @@
         <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Polissya Zhytomyr</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>8.4</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Polissya Zhytomyr</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>8.4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Digenis Ypsona</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="H11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.8</v>
       </c>
-      <c r="I11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,24 +2683,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Kapaz Ganja</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="n">
         <v>1.04</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Cypriot 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>Digenis Ypsona</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="H16" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="J16" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Al Ittihad (EGY)</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J17" t="n">
         <v>2.74</v>
       </c>
-      <c r="G17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.8</v>
+        <v>1.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,201 +3830,783 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 09:33:28</t>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pharco FC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>South African Premier Division</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>14:30:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Durban City</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Stellenbosch FC</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="G18" t="n">
+      <c r="F20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G20" t="n">
         <v>3.55</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="H20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I20" t="n">
         <v>3.7</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" t="n">
         <v>2.6</v>
       </c>
-      <c r="K18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="K20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-05-06 09:33:28</t>
+      <c r="Q20" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Polish I Liga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wisla Krakow</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-06 11:46:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G2" t="n">
         <v>3.15</v>
@@ -766,7 +766,7 @@
         <v>2.36</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J2" t="n">
         <v>3.6</v>
@@ -781,7 +781,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -790,22 +790,22 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R2" t="n">
         <v>1.48</v>
       </c>
       <c r="S2" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
         <v>1.46</v>
@@ -817,7 +817,7 @@
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
         <v>36</v>
@@ -856,13 +856,13 @@
         <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
@@ -981,7 +981,7 @@
         <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
         <v>1.81</v>
@@ -996,7 +996,7 @@
         <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
         <v>1.24</v>
@@ -1005,10 +1005,10 @@
         <v>1.95</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>40</v>
@@ -1017,10 +1017,10 @@
         <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
         <v>21</v>
@@ -1029,10 +1029,10 @@
         <v>65</v>
       </c>
       <c r="AF3" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>22</v>
@@ -1053,25 +1053,25 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO3" t="n">
         <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
@@ -1080,10 +1080,10 @@
         <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
         <v>1.03</v>
@@ -1092,7 +1092,7 @@
         <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
         <v>1.01</v>
@@ -1101,20 +1101,20 @@
         <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J4" t="n">
         <v>1.02</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1348,10 +1348,10 @@
         <v>2.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="K5" t="n">
         <v>3.3</v>
@@ -1360,7 +1360,7 @@
         <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
         <v>2.62</v>
@@ -1369,28 +1369,28 @@
         <v>1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
@@ -1408,7 +1408,7 @@
         <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
         <v>16.5</v>
@@ -1417,7 +1417,7 @@
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AG5" t="n">
         <v>17.5</v>
@@ -1456,7 +1456,7 @@
         <v>12.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1465,10 +1465,10 @@
         <v>5.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AX5" t="n">
         <v>14</v>
@@ -1480,29 +1480,29 @@
         <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
         <v>2.36</v>
@@ -1542,16 +1542,16 @@
         <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
         <v>3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="M6" t="n">
         <v>1.16</v>
@@ -1563,7 +1563,7 @@
         <v>1.66</v>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -1575,16 +1575,16 @@
         <v>6.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
         <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X6" t="n">
         <v>8.4</v>
@@ -1596,7 +1596,7 @@
         <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB6" t="n">
         <v>6.4</v>
@@ -1620,7 +1620,7 @@
         <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ6" t="n">
         <v>34</v>
@@ -1632,7 +1632,7 @@
         <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN6" t="n">
         <v>46</v>
@@ -1650,7 +1650,7 @@
         <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT6" t="n">
         <v>5.7</v>
@@ -1662,7 +1662,7 @@
         <v>17.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
@@ -1674,7 +1674,7 @@
         <v>7.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB6" t="n">
         <v>7.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
         <v>2.54</v>
@@ -1745,152 +1745,152 @@
         <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
         <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
@@ -1933,165 +1933,165 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Olympique Akbou</t>
+          <t>Polissya Zhytomyr</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.27</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>18.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Polissya Zhytomyr</t>
+          <t>Uta Arad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.21</v>
+        <v>1.93</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>1.14</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK10" t="n">
         <v>27</v>
       </c>
-      <c r="J10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>5.1</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>1.76</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FC Sabah</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kapaz Ganja</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M12" t="n">
         <v>1.04</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K12" t="n">
-        <v>950</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cypriot 1st Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Olympique Akbou</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Digenis Ypsona</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>FC Sabah</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Kapaz Ganja</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.41</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P14" t="n">
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>22</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.04</v>
       </c>
-      <c r="G15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K15" t="n">
-        <v>950</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Cukaricki</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>1.52</v>
       </c>
       <c r="G16" t="n">
-        <v>3.95</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I16" t="n">
-        <v>2.72</v>
+        <v>870</v>
       </c>
       <c r="J16" t="n">
         <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Rakow Czestochowa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Ittihad (EGY)</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.9</v>
       </c>
-      <c r="G17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P18" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>1.19</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ranheim IL</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.44</v>
+        <v>1.16</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>South African Premier Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,378 +4235,4452 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stellenbosch FC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.96</v>
+        <v>1.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 11:46:30</t>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hobro</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>B93 Copenhagen</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cypriot 1st Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Anorthosis</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Digenis Ypsona</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>KSV 1919</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>St Polten</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X23" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Rapid Vienna (Am)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>First Vienna Fc 1894</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FC Liefering</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Admira Wacker</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bregenz</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Austria Wien (A)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>WSC Hertha Wels</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SK Sturm Graz II</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>950</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Austrian Erste Liga</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SKU Amstetten</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Austria Klagenfurt</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>German Bundesliga 2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Karlsruhe</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X29" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>German Bundesliga 2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X30" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Algerian Ligue 1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>13:45:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Kabylie</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ES Setif</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K31" t="n">
+        <v>950</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Norwegian 1st Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ranheim IL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pharco FC</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bulgarian A League</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CSKA 1948 Sofia</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Danish 2nd Division</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Skive</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FC Helsingor</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K36" t="n">
+        <v>950</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AaB</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Middelfart</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>260</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>950</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Egyptian Premier</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Modern Sport FC</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Al Ittihad (EGY)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>South African Premier Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Durban City</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Stellenbosch FC</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Romanian Liga I</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CFR Cluj</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Polish Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lech Poznan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>28</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K41" t="n">
+        <v>950</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Polish I Liga</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>16:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Wisla Krakow</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Chrobry Glogow</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="F42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I42" t="n">
         <v>10.5</v>
       </c>
-      <c r="J21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="J42" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q42" t="n">
         <v>1.59</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-05-06 11:46:30</t>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:02:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
@@ -969,7 +969,7 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -984,7 +984,7 @@
         <v>1.79</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
         <v>1.31</v>
@@ -1095,7 +1095,7 @@
         <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BC3" t="n">
         <v>4.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1339,40 +1339,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G5" t="n">
         <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>1.41</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1381,16 +1381,16 @@
         <v>5.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
         <v>1.76</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
@@ -1465,7 +1465,7 @@
         <v>5.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
@@ -1474,7 +1474,7 @@
         <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="AZ5" t="n">
         <v>16</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.84</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
         <v>2.54</v>
@@ -1757,7 +1757,7 @@
         <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
         <v>2.18</v>
@@ -1778,7 +1778,7 @@
         <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1835,13 +1835,13 @@
         <v>40</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>3.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS7" t="n">
         <v>4.7</v>
@@ -1856,16 +1856,16 @@
         <v>3.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA7" t="n">
         <v>4.8</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H8" t="n">
         <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J8" t="n">
         <v>1.04</v>
@@ -1945,13 +1945,13 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q8" t="n">
         <v>1.15</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2124,10 +2124,10 @@
         <v>18.5</v>
       </c>
       <c r="I9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="K9" t="n">
         <v>7.8</v>
@@ -2139,7 +2139,7 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
         <v>1.27</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="G10" t="n">
         <v>2.16</v>
@@ -2351,10 +2351,10 @@
         <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
         <v>1.26</v>
@@ -2384,7 +2384,7 @@
         <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF10" t="n">
         <v>14</v>
@@ -2426,7 +2426,7 @@
         <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>7.2</v>
@@ -2450,7 +2450,7 @@
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
         <v>18.5</v>
@@ -2459,7 +2459,7 @@
         <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
         <v>5</v>
@@ -2468,11 +2468,11 @@
         <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2557,37 +2557,37 @@
         <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
         <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF11" t="n">
         <v>55</v>
       </c>
       <c r="AG11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>40</v>
@@ -2599,7 +2599,7 @@
         <v>85</v>
       </c>
       <c r="AL11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
         <v>120</v>
@@ -2608,10 +2608,10 @@
         <v>90</v>
       </c>
       <c r="AO11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.199999999999999</v>
@@ -2620,13 +2620,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
         <v>8.4</v>
@@ -2635,7 +2635,7 @@
         <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AY11" t="n">
         <v>17.5</v>
@@ -2644,29 +2644,29 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BG11" t="n">
         <v>6.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
         <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AP12" t="n">
         <v>18</v>
@@ -2814,7 +2814,7 @@
         <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT12" t="n">
         <v>11.5</v>
@@ -2832,25 +2832,25 @@
         <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="G15" t="n">
         <v>1.8</v>
@@ -3294,7 +3294,7 @@
         <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>9.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3315,7 +3315,7 @@
         <v>1.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
         <v>2.16</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3473,37 +3473,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
         <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.06</v>
+        <v>2.92</v>
       </c>
       <c r="O16" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
         <v>1.64</v>
@@ -3515,16 +3515,16 @@
         <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K19" t="n">
         <v>950</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>1.02</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H20" t="n">
         <v>1.02</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J20" t="n">
         <v>1.02</v>
@@ -4273,13 +4273,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O20" t="n">
         <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q20" t="n">
         <v>1.2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4476,7 @@
         <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R21" t="n">
         <v>1.42</v>
@@ -4500,7 +4500,7 @@
         <v>23</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
         <v>32</v>
@@ -4509,25 +4509,25 @@
         <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
         <v>50</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
         <v>55</v>
@@ -4545,7 +4545,7 @@
         <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AO21" t="n">
         <v>44</v>
@@ -4554,13 +4554,13 @@
         <v>5.9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AT21" t="n">
         <v>4.7</v>
@@ -4572,7 +4572,7 @@
         <v>3.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AX21" t="n">
         <v>5.1</v>
@@ -4584,7 +4584,7 @@
         <v>5.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BB21" t="n">
         <v>3.05</v>
@@ -4596,7 +4596,7 @@
         <v>2.02</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BF21" t="n">
         <v>8.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
         <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R23" t="n">
         <v>1.46</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
         <v>3.75</v>
@@ -5058,7 +5058,7 @@
         <v>2.26</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="R24" t="n">
         <v>1.52</v>
@@ -5070,7 +5070,7 @@
         <v>1.64</v>
       </c>
       <c r="U24" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V24" t="n">
         <v>1.85</v>
@@ -5094,7 +5094,7 @@
         <v>16.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD24" t="n">
         <v>11</v>
@@ -5124,7 +5124,7 @@
         <v>44</v>
       </c>
       <c r="AM24" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN24" t="n">
         <v>34</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G25" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H25" t="n">
         <v>2.4</v>
       </c>
       <c r="I25" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
         <v>4.3</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>2.12</v>
       </c>
       <c r="G28" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H28" t="n">
         <v>3.8</v>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.75</v>
@@ -5849,10 +5849,10 @@
         <v>1.93</v>
       </c>
       <c r="V28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X28" t="n">
         <v>16</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
         <v>3.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R29" t="n">
         <v>1.93</v>
@@ -6040,7 +6040,7 @@
         <v>1.6</v>
       </c>
       <c r="U29" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V29" t="n">
         <v>1.15</v>
@@ -6103,10 +6103,10 @@
         <v>60</v>
       </c>
       <c r="AP29" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="AR29" t="n">
         <v>10.5</v>
@@ -6154,11 +6154,11 @@
         <v>3.25</v>
       </c>
       <c r="BG29" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>2.26</v>
       </c>
       <c r="I30" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>3.85</v>
@@ -6228,13 +6228,13 @@
         <v>1.57</v>
       </c>
       <c r="S30" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="T30" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U30" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="V30" t="n">
         <v>1.73</v>
@@ -6258,7 +6258,7 @@
         <v>17.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD30" t="n">
         <v>12</v>
@@ -6276,7 +6276,7 @@
         <v>15</v>
       </c>
       <c r="AI30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ30" t="n">
         <v>50</v>
@@ -6333,16 +6333,16 @@
         <v>22</v>
       </c>
       <c r="BB30" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF30" t="n">
         <v>16</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="H32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I32" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="J32" t="n">
         <v>3.95</v>
@@ -6595,40 +6595,40 @@
         <v>4.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M32" t="n">
         <v>1.02</v>
       </c>
       <c r="N32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O32" t="n">
         <v>1.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T32" t="n">
         <v>1.45</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.46</v>
       </c>
       <c r="U32" t="n">
         <v>2.78</v>
       </c>
       <c r="V32" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="W32" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6643,10 +6643,10 @@
         <v>46</v>
       </c>
       <c r="AB32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AC32" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD32" t="n">
         <v>17</v>
@@ -6655,10 +6655,10 @@
         <v>30</v>
       </c>
       <c r="AF32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH32" t="n">
         <v>20</v>
@@ -6670,7 +6670,7 @@
         <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL32" t="n">
         <v>42</v>
@@ -6694,19 +6694,19 @@
         <v>13</v>
       </c>
       <c r="AS32" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
         <v>13</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
         <v>8</v>
       </c>
       <c r="AW32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX32" t="n">
         <v>16.5</v>
@@ -6718,13 +6718,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BA32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
         <v>16</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>16.5</v>
       </c>
       <c r="BD32" t="n">
         <v>18</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
         <v>1.01</v>
       </c>
       <c r="O33" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
@@ -6810,13 +6810,13 @@
         <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V33" t="n">
         <v>1.5</v>
@@ -6879,52 +6879,52 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
         <v>1.31</v>
       </c>
       <c r="M34" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
         <v>3.55</v>
@@ -7013,7 +7013,7 @@
         <v>2.06</v>
       </c>
       <c r="V34" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
         <v>1.59</v>
@@ -7022,7 +7022,7 @@
         <v>21</v>
       </c>
       <c r="Y34" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
         <v>26</v>
@@ -7031,13 +7031,13 @@
         <v>65</v>
       </c>
       <c r="AB34" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
         <v>10.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
         <v>38</v>
@@ -7046,19 +7046,19 @@
         <v>22</v>
       </c>
       <c r="AG34" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AI34" t="n">
         <v>55</v>
       </c>
       <c r="AJ34" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK34" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL34" t="n">
         <v>44</v>
@@ -7079,10 +7079,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT34" t="n">
         <v>9</v>
@@ -7094,7 +7094,7 @@
         <v>9.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AX34" t="n">
         <v>13</v>
@@ -7106,29 +7106,29 @@
         <v>11.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BB34" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD34" t="n">
         <v>3.95</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BE34" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE34" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG34" t="n">
         <v>3.8</v>
       </c>
-      <c r="BG34" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -7162,13 +7162,13 @@
         <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H35" t="n">
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J35" t="n">
         <v>1.04</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
         <v>3.7</v>
       </c>
       <c r="L36" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
         <v>1.07</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -7589,10 +7589,10 @@
         <v>2.34</v>
       </c>
       <c r="T37" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
@@ -7655,52 +7655,52 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
         <v>1.01</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>4.8</v>
       </c>
       <c r="G38" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H38" t="n">
         <v>1.53</v>
@@ -7768,13 +7768,13 @@
         <v>1.01</v>
       </c>
       <c r="O38" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P38" t="n">
         <v>2.46</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R38" t="n">
         <v>1.25</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -7959,13 +7959,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O39" t="n">
         <v>1.25</v>
       </c>
       <c r="P39" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q39" t="n">
         <v>1.25</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
         <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J40" t="n">
         <v>2.6</v>
@@ -8237,7 +8237,7 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.1</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>2.9</v>
       </c>
       <c r="G41" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H41" t="n">
         <v>2.96</v>
@@ -8335,7 +8335,7 @@
         <v>3.4</v>
       </c>
       <c r="J41" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K41" t="n">
         <v>3.05</v>
@@ -8401,7 +8401,7 @@
         <v>60</v>
       </c>
       <c r="AF41" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG41" t="n">
         <v>16</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -8550,13 +8550,13 @@
         <v>2.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="R42" t="n">
         <v>1.76</v>
       </c>
       <c r="S42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T42" t="n">
         <v>1.5</v>
@@ -8670,7 +8670,7 @@
         <v>19.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BF42" t="n">
         <v>5.7</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O43" t="n">
         <v>1.01</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
         <v>3.5</v>
       </c>
       <c r="I44" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J44" t="n">
         <v>5.1</v>
@@ -8941,16 +8941,16 @@
         <v>1.47</v>
       </c>
       <c r="R44" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S44" t="n">
         <v>2.02</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
         <v>1.72</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R45" t="n">
         <v>1.23</v>
@@ -9207,52 +9207,52 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF45" t="n">
         <v>1.01</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -9335,10 +9335,10 @@
         <v>2.52</v>
       </c>
       <c r="T46" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="U46" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V46" t="n">
         <v>1.19</v>
@@ -9371,22 +9371,22 @@
         <v>70</v>
       </c>
       <c r="AF46" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG46" t="n">
         <v>10.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI46" t="n">
         <v>65</v>
       </c>
       <c r="AJ46" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AK46" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AL46" t="n">
         <v>29</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         <v>1.61</v>
       </c>
       <c r="U47" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="V47" t="n">
         <v>1.06</v>
@@ -9565,10 +9565,10 @@
         <v>1000</v>
       </c>
       <c r="AF47" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AG47" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH47" t="n">
         <v>34</v>
@@ -9577,10 +9577,10 @@
         <v>120</v>
       </c>
       <c r="AJ47" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AK47" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AL47" t="n">
         <v>34</v>
@@ -9595,62 +9595,62 @@
         <v>140</v>
       </c>
       <c r="AP47" t="n">
-        <v>38</v>
+        <v>4.4</v>
       </c>
       <c r="AQ47" t="n">
-        <v>46</v>
+        <v>4.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>90</v>
+        <v>4.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT47" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="AU47" t="n">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="AV47" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="AW47" t="n">
-        <v>100</v>
+        <v>4.6</v>
       </c>
       <c r="AX47" t="n">
-        <v>9.199999999999999</v>
+        <v>3.55</v>
       </c>
       <c r="AY47" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ47" t="n">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA47" t="n">
-        <v>65</v>
+        <v>4.5</v>
       </c>
       <c r="BB47" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="BC47" t="n">
-        <v>9.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="BD47" t="n">
-        <v>20</v>
+        <v>4.1</v>
       </c>
       <c r="BE47" t="n">
-        <v>65</v>
+        <v>4.5</v>
       </c>
       <c r="BF47" t="n">
         <v>2.36</v>
       </c>
       <c r="BG47" t="n">
-        <v>80</v>
+        <v>4.5</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         <v>3.7</v>
       </c>
       <c r="J48" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="K48" t="n">
         <v>3.15</v>
@@ -9702,19 +9702,19 @@
         <v>1.01</v>
       </c>
       <c r="M48" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N48" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="O48" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P48" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="R48" t="n">
         <v>1.13</v>
@@ -9726,7 +9726,7 @@
         <v>1.01</v>
       </c>
       <c r="U48" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V48" t="n">
         <v>1.37</v>
@@ -9753,7 +9753,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD48" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE48" t="n">
         <v>1000</v>
@@ -9762,10 +9762,10 @@
         <v>25</v>
       </c>
       <c r="AG48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH48" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI48" t="n">
         <v>1000</v>
@@ -9792,7 +9792,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ48" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR48" t="n">
         <v>12</v>
@@ -9801,13 +9801,13 @@
         <v>1.03</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU48" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AV48" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW48" t="n">
         <v>1.03</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>3.75</v>
       </c>
       <c r="H49" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I49" t="n">
         <v>2.7</v>
@@ -9893,7 +9893,7 @@
         <v>3.5</v>
       </c>
       <c r="L49" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M49" t="n">
         <v>1.01</v>
@@ -9953,10 +9953,10 @@
         <v>46</v>
       </c>
       <c r="AF49" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH49" t="n">
         <v>29</v>
@@ -9968,7 +9968,7 @@
         <v>95</v>
       </c>
       <c r="AK49" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL49" t="n">
         <v>90</v>
@@ -9983,28 +9983,28 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AQ49" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AR49" t="n">
         <v>10.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AU49" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AX49" t="n">
         <v>16</v>
@@ -10013,32 +10013,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ49" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BB49" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BC49" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BD49" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BF49" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BG49" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -10069,19 +10069,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G50" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="H50" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I50" t="n">
         <v>6.8</v>
       </c>
       <c r="J50" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K50" t="n">
         <v>5.6</v>
@@ -10093,19 +10093,19 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O50" t="n">
         <v>1.15</v>
       </c>
       <c r="P50" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q50" t="n">
         <v>1.4</v>
       </c>
       <c r="R50" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S50" t="n">
         <v>2.12</v>
@@ -10114,13 +10114,13 @@
         <v>1.58</v>
       </c>
       <c r="U50" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V50" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W50" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="X50" t="n">
         <v>38</v>
@@ -10135,7 +10135,7 @@
         <v>140</v>
       </c>
       <c r="AB50" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC50" t="n">
         <v>14.5</v>
@@ -10159,46 +10159,46 @@
         <v>60</v>
       </c>
       <c r="AJ50" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK50" t="n">
         <v>17</v>
       </c>
       <c r="AL50" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM50" t="n">
         <v>75</v>
       </c>
       <c r="AN50" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO50" t="n">
         <v>55</v>
       </c>
       <c r="AP50" t="n">
-        <v>24</v>
+        <v>4.7</v>
       </c>
       <c r="AQ50" t="n">
-        <v>22</v>
+        <v>4.7</v>
       </c>
       <c r="AR50" t="n">
         <v>38</v>
       </c>
       <c r="AS50" t="n">
-        <v>90</v>
+        <v>5.2</v>
       </c>
       <c r="AT50" t="n">
         <v>10.5</v>
       </c>
       <c r="AU50" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV50" t="n">
         <v>17</v>
       </c>
       <c r="AW50" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="AX50" t="n">
         <v>10</v>
@@ -10222,7 +10222,7 @@
         <v>19</v>
       </c>
       <c r="BE50" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="BF50" t="n">
         <v>4.4</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10278,7 @@
         <v>3.5</v>
       </c>
       <c r="K51" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10299,16 +10299,16 @@
         <v>1.47</v>
       </c>
       <c r="R51" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="T51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U51" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V51" t="n">
         <v>1.92</v>
@@ -10371,52 +10371,52 @@
         <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE51" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF51" t="n">
         <v>1.01</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
         <v>6.4</v>
       </c>
       <c r="I52" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="J52" t="n">
         <v>4.8</v>
@@ -10493,7 +10493,7 @@
         <v>1.33</v>
       </c>
       <c r="R52" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S52" t="n">
         <v>1.87</v>
@@ -10565,52 +10565,52 @@
         <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE52" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF52" t="n">
         <v>1.01</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -10654,10 +10654,10 @@
         <v>2.94</v>
       </c>
       <c r="G53" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H53" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I53" t="n">
         <v>2.5</v>
@@ -10681,28 +10681,28 @@
         <v>1.21</v>
       </c>
       <c r="P53" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R53" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
         <v>2.38</v>
       </c>
       <c r="T53" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U53" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V53" t="n">
         <v>1.66</v>
       </c>
       <c r="W53" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10759,52 +10759,52 @@
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF53" t="n">
         <v>1.01</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -10878,25 +10878,25 @@
         <v>2.56</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="R54" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S54" t="n">
         <v>2.04</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V54" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="W54" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -10953,52 +10953,52 @@
         <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF54" t="n">
         <v>1.01</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -11039,55 +11039,55 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G55" t="n">
         <v>4.1</v>
       </c>
       <c r="H55" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J55" t="n">
         <v>3.55</v>
       </c>
       <c r="K55" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L55" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M55" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N55" t="n">
-        <v>1.87</v>
+        <v>3.6</v>
       </c>
       <c r="O55" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P55" t="n">
         <v>1.87</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="R55" t="n">
         <v>1.33</v>
       </c>
       <c r="S55" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T55" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U55" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V55" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W55" t="n">
         <v>1.32</v>
@@ -11096,7 +11096,7 @@
         <v>14.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z55" t="n">
         <v>14</v>
@@ -11114,7 +11114,7 @@
         <v>11.5</v>
       </c>
       <c r="AE55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF55" t="n">
         <v>30</v>
@@ -11129,10 +11129,10 @@
         <v>40</v>
       </c>
       <c r="AJ55" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AK55" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL55" t="n">
         <v>60</v>
@@ -11141,7 +11141,7 @@
         <v>120</v>
       </c>
       <c r="AN55" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO55" t="n">
         <v>18</v>
@@ -11156,7 +11156,7 @@
         <v>11</v>
       </c>
       <c r="AS55" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT55" t="n">
         <v>12</v>
@@ -11171,7 +11171,7 @@
         <v>19.5</v>
       </c>
       <c r="AX55" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AY55" t="n">
         <v>13.5</v>
@@ -11180,29 +11180,29 @@
         <v>6</v>
       </c>
       <c r="BA55" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB55" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BD55" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC55" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE55" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF55" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="BG55" t="n">
         <v>13</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -11266,13 +11266,13 @@
         <v>2.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="R56" t="n">
         <v>1.36</v>
       </c>
       <c r="S56" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="T56" t="n">
         <v>1.01</v>
@@ -11341,52 +11341,52 @@
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF56" t="n">
         <v>1.01</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
         <v>950</v>
       </c>
       <c r="L57" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M57" t="n">
         <v>1.01</v>
@@ -11469,13 +11469,13 @@
         <v>2.1</v>
       </c>
       <c r="T57" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W57" t="n">
         <v>2.8</v>
@@ -11535,52 +11535,52 @@
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ57" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AR57" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS57" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT57" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU57" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV57" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AW57" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX57" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY57" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ57" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA57" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB57" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC57" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD57" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE57" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF57" t="n">
         <v>1.01</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -11627,25 +11627,25 @@
         <v>1.97</v>
       </c>
       <c r="H58" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="I58" t="n">
         <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K58" t="n">
         <v>6.6</v>
       </c>
       <c r="L58" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M58" t="n">
         <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O58" t="n">
         <v>1.36</v>
@@ -11654,19 +11654,19 @@
         <v>1.24</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R58" t="n">
         <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="T58" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U58" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V58" t="n">
         <v>1.25</v>
@@ -11675,116 +11675,116 @@
         <v>2.02</v>
       </c>
       <c r="X58" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y58" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z58" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA58" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB58" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AC58" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD58" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF58" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AI58" t="n">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK58" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL58" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM58" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AN58" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO58" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="AP58" t="n">
-        <v>9.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ58" t="n">
-        <v>9.6</v>
+        <v>1.54</v>
       </c>
       <c r="AR58" t="n">
-        <v>20</v>
+        <v>1.55</v>
       </c>
       <c r="AS58" t="n">
-        <v>40</v>
+        <v>1.59</v>
       </c>
       <c r="AT58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU58" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU58" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV58" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW58" t="n">
-        <v>38</v>
+        <v>1.59</v>
       </c>
       <c r="AX58" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY58" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY58" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ58" t="n">
-        <v>16</v>
+        <v>1.56</v>
       </c>
       <c r="BA58" t="n">
-        <v>40</v>
+        <v>1.6</v>
       </c>
       <c r="BB58" t="n">
-        <v>17.5</v>
+        <v>1.54</v>
       </c>
       <c r="BC58" t="n">
-        <v>17</v>
+        <v>1.56</v>
       </c>
       <c r="BD58" t="n">
-        <v>30</v>
+        <v>1.59</v>
       </c>
       <c r="BE58" t="n">
-        <v>40</v>
+        <v>1.6</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G59" t="n">
         <v>1.75</v>
@@ -11824,7 +11824,7 @@
         <v>5</v>
       </c>
       <c r="I59" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J59" t="n">
         <v>4.4</v>
@@ -11833,13 +11833,13 @@
         <v>4.8</v>
       </c>
       <c r="L59" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M59" t="n">
         <v>1.01</v>
       </c>
       <c r="N59" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O59" t="n">
         <v>1.18</v>
@@ -11848,7 +11848,7 @@
         <v>2.56</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R59" t="n">
         <v>1.62</v>
@@ -11857,10 +11857,10 @@
         <v>2.32</v>
       </c>
       <c r="T59" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U59" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V59" t="n">
         <v>1.21</v>
@@ -11872,7 +11872,7 @@
         <v>26</v>
       </c>
       <c r="Y59" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z59" t="n">
         <v>50</v>
@@ -11929,7 +11929,7 @@
         <v>21</v>
       </c>
       <c r="AR59" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS59" t="n">
         <v>10</v>
@@ -11938,13 +11938,13 @@
         <v>11</v>
       </c>
       <c r="AU59" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV59" t="n">
         <v>18</v>
       </c>
       <c r="AW59" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX59" t="n">
         <v>11</v>
@@ -11956,7 +11956,7 @@
         <v>15</v>
       </c>
       <c r="BA59" t="n">
-        <v>9.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="BB59" t="n">
         <v>15</v>
@@ -11968,7 +11968,7 @@
         <v>22</v>
       </c>
       <c r="BE59" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF59" t="n">
         <v>5.9</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
         <v>1.28</v>
       </c>
       <c r="M60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N60" t="n">
         <v>2.28</v>
@@ -12045,7 +12045,7 @@
         <v>1.66</v>
       </c>
       <c r="R60" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="S60" t="n">
         <v>1.66</v>
@@ -12054,7 +12054,7 @@
         <v>1.01</v>
       </c>
       <c r="U60" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V60" t="n">
         <v>1.34</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -12203,61 +12203,61 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="G61" t="n">
         <v>1.73</v>
       </c>
       <c r="H61" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J61" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K61" t="n">
         <v>4.1</v>
       </c>
       <c r="L61" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M61" t="n">
         <v>1.08</v>
       </c>
       <c r="N61" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="O61" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P61" t="n">
         <v>1.8</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R61" t="n">
         <v>1.29</v>
       </c>
       <c r="S61" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T61" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U61" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V61" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W61" t="n">
         <v>2.36</v>
       </c>
       <c r="X61" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y61" t="n">
         <v>20</v>
@@ -12266,107 +12266,107 @@
         <v>50</v>
       </c>
       <c r="AA61" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB61" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD61" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE61" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF61" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG61" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH61" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI61" t="n">
         <v>130</v>
       </c>
       <c r="AJ61" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK61" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>21</v>
       </c>
       <c r="AL61" t="n">
         <v>46</v>
       </c>
       <c r="AM61" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN61" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO61" t="n">
         <v>160</v>
       </c>
       <c r="AP61" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AQ61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR61" t="n">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="AS61" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AT61" t="n">
         <v>6.2</v>
       </c>
       <c r="AU61" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV61" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW61" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="AX61" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY61" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ61" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA61" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BB61" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC61" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD61" t="n">
         <v>34</v>
       </c>
       <c r="BE61" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BF61" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BG61" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -12415,13 +12415,13 @@
         <v>4.6</v>
       </c>
       <c r="L62" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M62" t="n">
         <v>1.05</v>
       </c>
       <c r="N62" t="n">
-        <v>2.02</v>
+        <v>3.95</v>
       </c>
       <c r="O62" t="n">
         <v>1.27</v>
@@ -12433,16 +12433,16 @@
         <v>1.83</v>
       </c>
       <c r="R62" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S62" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="T62" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="U62" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="V62" t="n">
         <v>1.2</v>
@@ -12451,116 +12451,116 @@
         <v>2.4</v>
       </c>
       <c r="X62" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y62" t="n">
         <v>21</v>
       </c>
-      <c r="Y62" t="n">
-        <v>24</v>
-      </c>
       <c r="Z62" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AA62" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB62" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AC62" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE62" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO62" t="n">
         <v>95</v>
       </c>
-      <c r="AF62" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN62" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO62" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP62" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="AR62" t="n">
-        <v>2.44</v>
+        <v>7.2</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="AU62" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV62" t="n">
-        <v>2.32</v>
+        <v>6.2</v>
       </c>
       <c r="AW62" t="n">
-        <v>2.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX62" t="n">
-        <v>2.12</v>
+        <v>9</v>
       </c>
       <c r="AY62" t="n">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="AZ62" t="n">
-        <v>2.32</v>
+        <v>6.2</v>
       </c>
       <c r="BA62" t="n">
-        <v>2.48</v>
+        <v>7.8</v>
       </c>
       <c r="BB62" t="n">
-        <v>2.56</v>
+        <v>5.8</v>
       </c>
       <c r="BC62" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="BD62" t="n">
-        <v>2.42</v>
+        <v>7</v>
       </c>
       <c r="BE62" t="n">
-        <v>2.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF62" t="n">
-        <v>2.56</v>
+        <v>7.6</v>
       </c>
       <c r="BG62" t="n">
-        <v>2.56</v>
+        <v>8</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -12594,16 +12594,16 @@
         <v>1.68</v>
       </c>
       <c r="G63" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="H63" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I63" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J63" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K63" t="n">
         <v>4.5</v>
@@ -12612,37 +12612,37 @@
         <v>1.38</v>
       </c>
       <c r="M63" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N63" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O63" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P63" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q63" t="n">
         <v>1.93</v>
       </c>
       <c r="R63" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V63" t="n">
         <v>1.18</v>
       </c>
       <c r="W63" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="X63" t="n">
         <v>16</v>
@@ -12651,25 +12651,25 @@
         <v>19.5</v>
       </c>
       <c r="Z63" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA63" t="n">
         <v>190</v>
       </c>
       <c r="AB63" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC63" t="n">
         <v>9.6</v>
       </c>
       <c r="AD63" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE63" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF63" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG63" t="n">
         <v>10.5</v>
@@ -12681,7 +12681,7 @@
         <v>100</v>
       </c>
       <c r="AJ63" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="n">
         <v>19</v>
@@ -12705,7 +12705,7 @@
         <v>16</v>
       </c>
       <c r="AR63" t="n">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="AS63" t="n">
         <v>7.8</v>
@@ -12717,7 +12717,7 @@
         <v>8</v>
       </c>
       <c r="AV63" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="AW63" t="n">
         <v>7.4</v>
@@ -12732,7 +12732,7 @@
         <v>6</v>
       </c>
       <c r="BA63" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB63" t="n">
         <v>15</v>
@@ -12741,20 +12741,20 @@
         <v>15.5</v>
       </c>
       <c r="BD63" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE63" t="n">
         <v>7.8</v>
       </c>
       <c r="BF63" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG63" t="n">
         <v>7.6</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -12791,22 +12791,22 @@
         <v>1.8</v>
       </c>
       <c r="H64" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I64" t="n">
         <v>5.5</v>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K64" t="n">
         <v>4.6</v>
       </c>
       <c r="L64" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M64" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N64" t="n">
         <v>4.4</v>
@@ -12821,16 +12821,16 @@
         <v>1.7</v>
       </c>
       <c r="R64" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S64" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="T64" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U64" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V64" t="n">
         <v>1.22</v>
@@ -12839,116 +12839,116 @@
         <v>2.22</v>
       </c>
       <c r="X64" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="Y64" t="n">
         <v>25</v>
       </c>
       <c r="Z64" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA64" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB64" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV64" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX64" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA64" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC64" t="n">
         <v>14.5</v>
       </c>
-      <c r="AC64" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO64" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP64" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AS64" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AT64" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX64" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB64" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BD64" t="n">
-        <v>2.58</v>
+        <v>6</v>
       </c>
       <c r="BE64" t="n">
-        <v>2.78</v>
+        <v>7</v>
       </c>
       <c r="BF64" t="n">
-        <v>2.78</v>
+        <v>6.6</v>
       </c>
       <c r="BG64" t="n">
-        <v>2.78</v>
+        <v>6.6</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -12982,31 +12982,31 @@
         <v>3.65</v>
       </c>
       <c r="G65" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H65" t="n">
         <v>2.18</v>
       </c>
       <c r="I65" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K65" t="n">
         <v>3.5</v>
       </c>
       <c r="L65" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M65" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N65" t="n">
         <v>3.05</v>
       </c>
       <c r="O65" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P65" t="n">
         <v>1.68</v>
@@ -13015,16 +13015,16 @@
         <v>2.24</v>
       </c>
       <c r="R65" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S65" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T65" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U65" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V65" t="n">
         <v>1.76</v>
@@ -13075,7 +13075,7 @@
         <v>60</v>
       </c>
       <c r="AL65" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM65" t="n">
         <v>150</v>
@@ -13135,14 +13135,14 @@
         <v>10.5</v>
       </c>
       <c r="BF65" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="BG65" t="n">
         <v>21</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
         <v>1.67</v>
       </c>
       <c r="G66" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H66" t="n">
         <v>5</v>
@@ -13188,10 +13188,10 @@
         <v>4.1</v>
       </c>
       <c r="K66" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L66" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M66" t="n">
         <v>1.01</v>
@@ -13215,10 +13215,10 @@
         <v>1.69</v>
       </c>
       <c r="T66" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U66" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V66" t="n">
         <v>1.21</v>
@@ -13227,7 +13227,7 @@
         <v>2.28</v>
       </c>
       <c r="X66" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Y66" t="n">
         <v>26</v>
@@ -13251,7 +13251,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG66" t="n">
         <v>12.5</v>
@@ -13275,68 +13275,68 @@
         <v>1000</v>
       </c>
       <c r="AN66" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO66" t="n">
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>2.44</v>
+        <v>16</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AR66" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="AU66" t="n">
-        <v>2.22</v>
+        <v>8</v>
       </c>
       <c r="AV66" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AW66" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="AX66" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="AY66" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="AZ66" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="BA66" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="BB66" t="n">
-        <v>2.46</v>
+        <v>14.5</v>
       </c>
       <c r="BC66" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="BD66" t="n">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="BE66" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="BF66" t="n">
-        <v>2.72</v>
+        <v>5.8</v>
       </c>
       <c r="BG66" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G67" t="n">
         <v>1.55</v>
@@ -13376,7 +13376,7 @@
         <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J67" t="n">
         <v>5.3</v>
@@ -13400,7 +13400,7 @@
         <v>3.4</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R67" t="n">
         <v>1.97</v>
@@ -13415,7 +13415,7 @@
         <v>2.76</v>
       </c>
       <c r="V67" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W67" t="n">
         <v>2.8</v>
@@ -13439,13 +13439,13 @@
         <v>13.5</v>
       </c>
       <c r="AD67" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE67" t="n">
         <v>60</v>
       </c>
       <c r="AF67" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AG67" t="n">
         <v>10.5</v>
@@ -13454,7 +13454,7 @@
         <v>17.5</v>
       </c>
       <c r="AI67" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ67" t="n">
         <v>17</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -13567,10 +13567,10 @@
         <v>2.88</v>
       </c>
       <c r="H68" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J68" t="n">
         <v>3.4</v>
@@ -13579,7 +13579,7 @@
         <v>3.5</v>
       </c>
       <c r="L68" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M68" t="n">
         <v>1.06</v>
@@ -13597,16 +13597,16 @@
         <v>1.75</v>
       </c>
       <c r="R68" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S68" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="T68" t="n">
         <v>1.49</v>
       </c>
       <c r="U68" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V68" t="n">
         <v>1.5</v>
@@ -13618,103 +13618,103 @@
         <v>19</v>
       </c>
       <c r="Y68" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z68" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA68" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB68" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC68" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE68" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF68" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH68" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AI68" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ68" t="n">
         <v>42</v>
       </c>
-      <c r="AJ68" t="n">
-        <v>46</v>
-      </c>
       <c r="AK68" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL68" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM68" t="n">
         <v>75</v>
       </c>
       <c r="AN68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO68" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP68" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ68" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>10.5</v>
       </c>
       <c r="AR68" t="n">
         <v>15</v>
       </c>
       <c r="AS68" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AT68" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU68" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV68" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AW68" t="n">
-        <v>4.6</v>
+        <v>24</v>
       </c>
       <c r="AX68" t="n">
         <v>15.5</v>
       </c>
       <c r="AY68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ68" t="n">
         <v>13</v>
       </c>
       <c r="BA68" t="n">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="BB68" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC68" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BD68" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE68" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="BF68" t="n">
         <v>14.5</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G69" t="n">
         <v>2.58</v>
@@ -13797,13 +13797,13 @@
         <v>3.6</v>
       </c>
       <c r="T69" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U69" t="n">
         <v>2.22</v>
       </c>
       <c r="V69" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W69" t="n">
         <v>1.63</v>
@@ -13884,7 +13884,7 @@
         <v>12.5</v>
       </c>
       <c r="AW69" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX69" t="n">
         <v>15</v>
@@ -13896,29 +13896,29 @@
         <v>16</v>
       </c>
       <c r="BA69" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB69" t="n">
         <v>32</v>
       </c>
       <c r="BC69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD69" t="n">
         <v>36</v>
       </c>
       <c r="BE69" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BF69" t="n">
         <v>20</v>
       </c>
       <c r="BG69" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -13961,158 +13961,158 @@
         <v>2.14</v>
       </c>
       <c r="J70" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K70" t="n">
         <v>3.65</v>
       </c>
       <c r="L70" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M70" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N70" t="n">
-        <v>1.77</v>
+        <v>3.3</v>
       </c>
       <c r="O70" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P70" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q70" t="n">
         <v>2.14</v>
       </c>
       <c r="R70" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S70" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="T70" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U70" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V70" t="n">
         <v>1.87</v>
       </c>
       <c r="W70" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X70" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD70" t="n">
         <v>11</v>
       </c>
-      <c r="Z70" t="n">
+      <c r="AE70" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG70" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA70" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC70" t="n">
+      <c r="AH70" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP70" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD70" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE70" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF70" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG70" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH70" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI70" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ70" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK70" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL70" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM70" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN70" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO70" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP70" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AQ70" t="n">
-        <v>2.14</v>
+        <v>7.4</v>
       </c>
       <c r="AR70" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC70" t="n">
         <v>9</v>
       </c>
-      <c r="AS70" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT70" t="n">
+      <c r="BD70" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF70" t="n">
         <v>9.6</v>
       </c>
-      <c r="AU70" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV70" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AW70" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AX70" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AY70" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AZ70" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BA70" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BB70" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BC70" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BD70" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BE70" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF70" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BG70" t="n">
-        <v>2.66</v>
+        <v>14</v>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -14161,16 +14161,16 @@
         <v>4.7</v>
       </c>
       <c r="L71" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M71" t="n">
         <v>1.01</v>
       </c>
       <c r="N71" t="n">
-        <v>3.55</v>
+        <v>1.99</v>
       </c>
       <c r="O71" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P71" t="n">
         <v>1.99</v>
@@ -14185,10 +14185,10 @@
         <v>2.84</v>
       </c>
       <c r="T71" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U71" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V71" t="n">
         <v>1.11</v>
@@ -14245,68 +14245,68 @@
         <v>1000</v>
       </c>
       <c r="AN71" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO71" t="n">
         <v>1000</v>
       </c>
       <c r="AP71" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AQ71" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="AR71" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="AS71" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="AT71" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AU71" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="AV71" t="n">
         <v>19</v>
       </c>
       <c r="AW71" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AX71" t="n">
         <v>2.2</v>
       </c>
-      <c r="AX71" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AY71" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="AZ71" t="n">
-        <v>2.06</v>
+        <v>2.46</v>
       </c>
       <c r="BA71" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="BB71" t="n">
         <v>10</v>
       </c>
       <c r="BC71" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="BD71" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="BE71" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="BF71" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG71" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -14337,16 +14337,16 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="G72" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H72" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="I72" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>3.45</v>
@@ -14358,19 +14358,19 @@
         <v>1.36</v>
       </c>
       <c r="M72" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N72" t="n">
-        <v>1.88</v>
+        <v>3.65</v>
       </c>
       <c r="O72" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P72" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R72" t="n">
         <v>1.33</v>
@@ -14379,31 +14379,31 @@
         <v>3.35</v>
       </c>
       <c r="T72" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="U72" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V72" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W72" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X72" t="n">
         <v>17</v>
       </c>
       <c r="Y72" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z72" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA72" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AB72" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC72" t="n">
         <v>9.4</v>
@@ -14412,28 +14412,28 @@
         <v>14</v>
       </c>
       <c r="AE72" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF72" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH72" t="n">
         <v>21</v>
       </c>
-      <c r="AG72" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AI72" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AJ72" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK72" t="n">
         <v>34</v>
       </c>
       <c r="AL72" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM72" t="n">
         <v>110</v>
@@ -14451,46 +14451,46 @@
         <v>9.4</v>
       </c>
       <c r="AR72" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AS72" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="AT72" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU72" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV72" t="n">
         <v>9.4</v>
       </c>
       <c r="AW72" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX72" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AY72" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ72" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA72" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB72" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BC72" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="BD72" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE72" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF72" t="n">
         <v>21</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -14549,13 +14549,13 @@
         <v>3.55</v>
       </c>
       <c r="L73" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M73" t="n">
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>1.74</v>
+        <v>2.68</v>
       </c>
       <c r="O73" t="n">
         <v>1.36</v>
@@ -14573,10 +14573,10 @@
         <v>3.35</v>
       </c>
       <c r="T73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U73" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V73" t="n">
         <v>1.69</v>
@@ -14639,52 +14639,52 @@
         <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ73" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR73" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS73" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT73" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU73" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV73" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW73" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX73" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY73" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ73" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA73" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB73" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC73" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BD73" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE73" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF73" t="n">
         <v>1.01</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -14749,16 +14749,16 @@
         <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O74" t="n">
         <v>1.38</v>
       </c>
       <c r="P74" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R74" t="n">
         <v>1.21</v>
@@ -14767,10 +14767,10 @@
         <v>3.35</v>
       </c>
       <c r="T74" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U74" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V74" t="n">
         <v>1.37</v>
@@ -14833,52 +14833,52 @@
         <v>1000</v>
       </c>
       <c r="AP74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE74" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF74" t="n">
         <v>1.01</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -15027,52 +15027,52 @@
         <v>1000</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE75" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF75" t="n">
         <v>1.01</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -15221,52 +15221,52 @@
         <v>1000</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE76" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF76" t="n">
         <v>1.01</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15349,7 @@
         <v>2.74</v>
       </c>
       <c r="T77" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U77" t="n">
         <v>1.01</v>
@@ -15415,52 +15415,52 @@
         <v>1000</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE77" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF77" t="n">
         <v>1.01</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -15501,16 +15501,16 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G78" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H78" t="n">
         <v>8</v>
       </c>
       <c r="I78" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J78" t="n">
         <v>5.4</v>
@@ -15519,7 +15519,7 @@
         <v>5.6</v>
       </c>
       <c r="L78" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M78" t="n">
         <v>1.03</v>
@@ -15537,7 +15537,7 @@
         <v>1.56</v>
       </c>
       <c r="R78" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S78" t="n">
         <v>2.36</v>
@@ -15549,7 +15549,7 @@
         <v>2.12</v>
       </c>
       <c r="V78" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W78" t="n">
         <v>3.2</v>
@@ -15564,7 +15564,7 @@
         <v>80</v>
       </c>
       <c r="AA78" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AB78" t="n">
         <v>11.5</v>
@@ -15573,7 +15573,7 @@
         <v>12.5</v>
       </c>
       <c r="AD78" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE78" t="n">
         <v>110</v>
@@ -15582,13 +15582,13 @@
         <v>10.5</v>
       </c>
       <c r="AG78" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AH78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI78" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ78" t="n">
         <v>13</v>
@@ -15606,7 +15606,7 @@
         <v>5.1</v>
       </c>
       <c r="AO78" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP78" t="n">
         <v>23</v>
@@ -15615,7 +15615,7 @@
         <v>30</v>
       </c>
       <c r="AR78" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS78" t="n">
         <v>15</v>
@@ -15630,7 +15630,7 @@
         <v>27</v>
       </c>
       <c r="AW78" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AX78" t="n">
         <v>9</v>
@@ -15642,7 +15642,7 @@
         <v>20</v>
       </c>
       <c r="BA78" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BB78" t="n">
         <v>11.5</v>
@@ -15654,17 +15654,17 @@
         <v>25</v>
       </c>
       <c r="BE78" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF78" t="n">
         <v>4.8</v>
       </c>
       <c r="BG78" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G79" t="n">
         <v>2.32</v>
@@ -15707,10 +15707,10 @@
         <v>5.6</v>
       </c>
       <c r="J79" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="K79" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="L79" t="n">
         <v>1.01</v>
@@ -15719,13 +15719,13 @@
         <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O79" t="n">
         <v>1.31</v>
       </c>
       <c r="P79" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q79" t="n">
         <v>1.92</v>
@@ -15737,7 +15737,7 @@
         <v>3</v>
       </c>
       <c r="T79" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U79" t="n">
         <v>1.01</v>
@@ -15803,52 +15803,52 @@
         <v>1000</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE79" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF79" t="n">
         <v>1.01</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -15889,13 +15889,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="G80" t="n">
         <v>1.25</v>
       </c>
       <c r="H80" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="I80" t="n">
         <v>20</v>
@@ -15907,13 +15907,13 @@
         <v>950</v>
       </c>
       <c r="L80" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M80" t="n">
         <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O80" t="n">
         <v>1.15</v>
@@ -15931,10 +15931,10 @@
         <v>2.08</v>
       </c>
       <c r="T80" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U80" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V80" t="n">
         <v>1.05</v>
@@ -15997,52 +15997,52 @@
         <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ80" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AR80" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS80" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT80" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU80" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV80" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AW80" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX80" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY80" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ80" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BA80" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB80" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC80" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BD80" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE80" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF80" t="n">
         <v>1.01</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -16089,7 +16089,7 @@
         <v>1.62</v>
       </c>
       <c r="H81" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I81" t="n">
         <v>10.5</v>
@@ -16107,13 +16107,13 @@
         <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="O81" t="n">
         <v>1.21</v>
       </c>
       <c r="P81" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q81" t="n">
         <v>1.59</v>
@@ -16125,10 +16125,10 @@
         <v>2.4</v>
       </c>
       <c r="T81" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U81" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V81" t="n">
         <v>1.1</v>
@@ -16191,52 +16191,52 @@
         <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE81" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF81" t="n">
         <v>1.01</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -16280,13 +16280,13 @@
         <v>2.62</v>
       </c>
       <c r="G82" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H82" t="n">
         <v>3</v>
       </c>
       <c r="I82" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>3.45</v>
@@ -16295,34 +16295,34 @@
         <v>3.5</v>
       </c>
       <c r="L82" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M82" t="n">
         <v>1.08</v>
       </c>
       <c r="N82" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O82" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P82" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R82" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S82" t="n">
         <v>3.6</v>
       </c>
       <c r="T82" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U82" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V82" t="n">
         <v>1.48</v>
@@ -16337,7 +16337,7 @@
         <v>12</v>
       </c>
       <c r="Z82" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA82" t="n">
         <v>48</v>
@@ -16376,7 +16376,7 @@
         <v>42</v>
       </c>
       <c r="AM82" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN82" t="n">
         <v>25</v>
@@ -16394,10 +16394,10 @@
         <v>17.5</v>
       </c>
       <c r="AS82" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT82" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU82" t="n">
         <v>7.2</v>
@@ -16427,10 +16427,10 @@
         <v>26</v>
       </c>
       <c r="BD82" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE82" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF82" t="n">
         <v>22</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -16489,16 +16489,16 @@
         <v>950</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P83" t="n">
         <v>2.74</v>
@@ -16507,134 +16507,134 @@
         <v>1.3</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -16665,10 +16665,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G84" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H84" t="n">
         <v>4.3</v>
@@ -16683,152 +16683,152 @@
         <v>5.4</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P84" t="n">
         <v>2.92</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK84" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AL84" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM84" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN84" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AO84" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP84" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR84" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AS84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU84" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX84" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY84" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ84" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB84" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC84" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD84" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BE84" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF84" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BG84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -16862,31 +16862,31 @@
         <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H85" t="n">
         <v>2.98</v>
       </c>
       <c r="I85" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J85" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="K85" t="n">
         <v>5.8</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P85" t="n">
         <v>3.4</v>
@@ -16895,134 +16895,134 @@
         <v>1.33</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK85" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL85" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AM85" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AN85" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AO85" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AP85" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR85" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AS85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU85" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY85" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ85" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB85" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC85" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD85" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BE85" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BF85" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG85" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
         <v>1.79</v>
       </c>
       <c r="I86" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J86" t="n">
         <v>4.8</v>
@@ -17071,152 +17071,152 @@
         <v>5.9</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="P86" t="n">
         <v>5.2</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI86" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK86" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL86" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AM86" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN86" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AO86" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU86" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AV86" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW86" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AX86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY86" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ86" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA86" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BB86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF86" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG86" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-05-06 16:19:40</t>
+          <t>2026-05-06 18:35:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-08.xlsx
@@ -778,7 +778,7 @@
         <v>1.31</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -799,10 +799,10 @@
         <v>2.94</v>
       </c>
       <c r="T2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
         <v>6.6</v>
@@ -1160,10 +1160,10 @@
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1178,7 +1178,7 @@
         <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R4" t="n">
         <v>1.31</v>
@@ -1196,7 +1196,7 @@
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1205,7 +1205,7 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1217,16 +1217,16 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>25</v>
@@ -1259,7 +1259,7 @@
         <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS4" t="n">
         <v>5</v>
@@ -1268,16 +1268,16 @@
         <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AY4" t="n">
         <v>8.199999999999999</v>
@@ -1292,23 +1292,23 @@
         <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE4" t="n">
         <v>5</v>
       </c>
       <c r="BF4" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>3.85</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
         <v>1.55</v>
@@ -1351,40 +1351,40 @@
         <v>2.14</v>
       </c>
       <c r="J5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
         <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.87</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="n">
         <v>2.6</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O6" t="n">
         <v>1.52</v>
@@ -1644,25 +1644,25 @@
         <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>3.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
         <v>14</v>
@@ -1671,7 +1671,7 @@
         <v>3.55</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>3.75</v>
       </c>
       <c r="BA6" t="n">
         <v>4.1</v>
@@ -1680,7 +1680,7 @@
         <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
         <v>4.2</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1802,10 +1802,10 @@
         <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
@@ -1856,7 +1856,7 @@
         <v>17.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -1865,19 +1865,19 @@
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BA7" t="n">
         <v>10</v>
       </c>
       <c r="BB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC7" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BD7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE7" t="n">
         <v>10.5</v>
@@ -1886,11 +1886,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.84</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
         <v>2.54</v>
@@ -1939,7 +1939,7 @@
         <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1960,7 +1960,7 @@
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
         <v>1.87</v>
@@ -1972,7 +1972,7 @@
         <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2029,7 +2029,7 @@
         <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>3.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2420,37 +2420,37 @@
         <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
         <v>6</v>
@@ -2459,20 +2459,20 @@
         <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
@@ -2545,16 +2545,16 @@
         <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V11" t="n">
         <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X11" t="n">
         <v>14.5</v>
@@ -2611,22 +2611,22 @@
         <v>85</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>13.5</v>
@@ -2638,35 +2638,35 @@
         <v>9.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD11" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
         <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
         <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U13" t="n">
         <v>2.48</v>
@@ -2981,7 +2981,7 @@
         <v>34</v>
       </c>
       <c r="AJ13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
@@ -3008,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT13" t="n">
         <v>11.5</v>
@@ -3032,7 +3032,7 @@
         <v>11.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
         <v>4.9</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
         <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
@@ -3127,10 +3127,10 @@
         <v>1.53</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3288,10 +3288,10 @@
         <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -3303,7 +3303,7 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
@@ -3318,13 +3318,13 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H19" t="n">
         <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K19" t="n">
         <v>950</v>
@@ -4079,7 +4079,7 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="O19" t="n">
         <v>1.19</v>
@@ -4088,19 +4088,19 @@
         <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>990</v>
       </c>
       <c r="J21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K21" t="n">
         <v>950</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4661,10 +4661,10 @@
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P22" t="n">
         <v>2.18</v>
@@ -4673,7 +4673,7 @@
         <v>1.68</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
         <v>2.54</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>3.4</v>
       </c>
       <c r="H23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>2.18</v>
@@ -4846,7 +4846,7 @@
         <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v>2.22</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R24" t="n">
         <v>1.46</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
         <v>4.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,7 +5243,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="O25" t="n">
         <v>1.21</v>
@@ -5261,16 +5261,16 @@
         <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G26" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="H26" t="n">
         <v>2.4</v>
       </c>
       <c r="I26" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="J26" t="n">
         <v>3.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>3.3</v>
       </c>
       <c r="H27" t="n">
-        <v>1.45</v>
+        <v>2.36</v>
       </c>
       <c r="I27" t="n">
         <v>3.85</v>
@@ -5622,7 +5622,7 @@
         <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>4.4</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>3.7</v>
@@ -5849,7 +5849,7 @@
         <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W28" t="n">
         <v>2.06</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6019,10 +6019,10 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P29" t="n">
         <v>1.72</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6422,7 @@
         <v>1.57</v>
       </c>
       <c r="S31" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="T31" t="n">
         <v>1.57</v>
@@ -6533,7 +6533,7 @@
         <v>9.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE31" t="n">
         <v>11</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6774,13 +6774,13 @@
         <v>2.72</v>
       </c>
       <c r="G33" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H33" t="n">
         <v>2.28</v>
       </c>
       <c r="I33" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J33" t="n">
         <v>3.95</v>
@@ -6792,7 +6792,7 @@
         <v>1.21</v>
       </c>
       <c r="M33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N33" t="n">
         <v>6.2</v>
@@ -6804,10 +6804,10 @@
         <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="R33" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="S33" t="n">
         <v>2.04</v>
@@ -6819,10 +6819,10 @@
         <v>2.78</v>
       </c>
       <c r="V33" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="G34" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="H34" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I34" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="J34" t="n">
         <v>3.35</v>
       </c>
       <c r="K34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L34" t="n">
         <v>1.31</v>
@@ -6995,7 +6995,7 @@
         <v>1.28</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q34" t="n">
         <v>1.76</v>
@@ -7013,10 +7013,10 @@
         <v>2.06</v>
       </c>
       <c r="V34" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="X34" t="n">
         <v>21</v>
@@ -7031,7 +7031,7 @@
         <v>65</v>
       </c>
       <c r="AB34" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC34" t="n">
         <v>10.5</v>
@@ -7058,7 +7058,7 @@
         <v>44</v>
       </c>
       <c r="AK34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL34" t="n">
         <v>44</v>
@@ -7073,13 +7073,13 @@
         <v>30</v>
       </c>
       <c r="AP34" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="AQ34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AS34" t="n">
         <v>4</v>
@@ -7094,7 +7094,7 @@
         <v>9.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX34" t="n">
         <v>13</v>
@@ -7106,29 +7106,29 @@
         <v>11.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BG34" t="n">
         <v>3.85</v>
       </c>
-      <c r="BD34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -7583,13 +7583,13 @@
         <v>1.96</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
         <v>3.35</v>
       </c>
       <c r="T37" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U37" t="n">
         <v>2.12</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -7777,10 +7777,10 @@
         <v>1.64</v>
       </c>
       <c r="R38" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S38" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="T38" t="n">
         <v>1.57</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>7.6</v>
       </c>
       <c r="H39" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I39" t="n">
         <v>1.67</v>
@@ -7950,7 +7950,7 @@
         <v>4.5</v>
       </c>
       <c r="K39" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,7 +7959,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O39" t="n">
         <v>1.16</v>
@@ -7971,22 +7971,22 @@
         <v>1.48</v>
       </c>
       <c r="R39" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S39" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V39" t="n">
         <v>2.48</v>
       </c>
       <c r="W39" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
         <v>3.45</v>
       </c>
       <c r="K40" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8153,7 +8153,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="O40" t="n">
         <v>1.26</v>
@@ -8165,13 +8165,13 @@
         <v>1.82</v>
       </c>
       <c r="R40" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U40" t="n">
         <v>2.08</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>2.96</v>
       </c>
       <c r="G41" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="H41" t="n">
         <v>2.72</v>
@@ -8335,7 +8335,7 @@
         <v>3.05</v>
       </c>
       <c r="J41" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="K41" t="n">
         <v>3.35</v>
@@ -8347,7 +8347,7 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.54</v>
+        <v>2.28</v>
       </c>
       <c r="O41" t="n">
         <v>1.02</v>
@@ -8365,16 +8365,16 @@
         <v>4.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U41" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V41" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X41" t="n">
         <v>10.5</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
         <v>8</v>
       </c>
       <c r="BC42" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="BD42" t="n">
         <v>8.6</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="G43" t="n">
         <v>1.88</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>1.02</v>
       </c>
       <c r="G44" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H44" t="n">
         <v>1.02</v>
@@ -8917,7 +8917,7 @@
         <v>1000</v>
       </c>
       <c r="J44" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K44" t="n">
         <v>950</v>
@@ -8929,7 +8929,7 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O44" t="n">
         <v>1.01</v>
@@ -8944,13 +8944,13 @@
         <v>1.24</v>
       </c>
       <c r="S44" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G46" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H46" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I46" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="J46" t="n">
         <v>3.15</v>
       </c>
       <c r="K46" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9323,7 +9323,7 @@
         <v>1.39</v>
       </c>
       <c r="P46" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q46" t="n">
         <v>2.16</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
         <v>2.52</v>
       </c>
       <c r="T47" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U47" t="n">
         <v>2.22</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -9705,22 +9705,22 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="O48" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="P48" t="n">
         <v>3.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R48" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="S48" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="T48" t="n">
         <v>1.61</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
         <v>2.84</v>
       </c>
       <c r="G49" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H49" t="n">
         <v>2.92</v>
@@ -9980,7 +9980,7 @@
         <v>80</v>
       </c>
       <c r="AO49" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AP49" t="n">
         <v>5.6</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -10117,10 +10117,10 @@
         <v>1.65</v>
       </c>
       <c r="V50" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W50" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X50" t="n">
         <v>14.5</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
         <v>1.73</v>
       </c>
       <c r="S51" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T51" t="n">
         <v>1.59</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
         <v>2.86</v>
       </c>
       <c r="G54" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="H54" t="n">
         <v>2.22</v>
@@ -10857,7 +10857,7 @@
         <v>2.5</v>
       </c>
       <c r="J54" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K54" t="n">
         <v>4.4</v>
@@ -10875,7 +10875,7 @@
         <v>1.21</v>
       </c>
       <c r="P54" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q54" t="n">
         <v>1.61</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="G55" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="H55" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I55" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="J55" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="K55" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11063,19 +11063,19 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="O55" t="n">
         <v>1.16</v>
       </c>
       <c r="P55" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="R55" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S55" t="n">
         <v>2.04</v>
@@ -11087,10 +11087,10 @@
         <v>1.11</v>
       </c>
       <c r="V55" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W55" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
         <v>1.6</v>
       </c>
       <c r="G56" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H56" t="n">
         <v>6</v>
@@ -11260,7 +11260,7 @@
         <v>4.3</v>
       </c>
       <c r="O56" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P56" t="n">
         <v>2.16</v>
@@ -11269,7 +11269,7 @@
         <v>1.76</v>
       </c>
       <c r="R56" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
         <v>2.96</v>
@@ -11287,7 +11287,7 @@
         <v>2.56</v>
       </c>
       <c r="X56" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y56" t="n">
         <v>25</v>
@@ -11311,16 +11311,16 @@
         <v>90</v>
       </c>
       <c r="AF56" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH56" t="n">
         <v>21</v>
       </c>
       <c r="AI56" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ56" t="n">
         <v>14.5</v>
@@ -11347,10 +11347,10 @@
         <v>20</v>
       </c>
       <c r="AR56" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS56" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AT56" t="n">
         <v>8.4</v>
@@ -11362,7 +11362,7 @@
         <v>20</v>
       </c>
       <c r="AW56" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX56" t="n">
         <v>9.199999999999999</v>
@@ -11374,7 +11374,7 @@
         <v>17.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BB56" t="n">
         <v>12.5</v>
@@ -11392,11 +11392,11 @@
         <v>6.2</v>
       </c>
       <c r="BG56" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -11621,10 +11621,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G58" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H58" t="n">
         <v>2.06</v>
@@ -11633,16 +11633,16 @@
         <v>2.08</v>
       </c>
       <c r="J58" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K58" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
       </c>
       <c r="M58" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N58" t="n">
         <v>3.55</v>
@@ -11654,7 +11654,7 @@
         <v>1.85</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="R58" t="n">
         <v>1.33</v>
@@ -11663,7 +11663,7 @@
         <v>3.4</v>
       </c>
       <c r="T58" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U58" t="n">
         <v>2.08</v>
@@ -11672,7 +11672,7 @@
         <v>1.92</v>
       </c>
       <c r="W58" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X58" t="n">
         <v>13.5</v>
@@ -11729,7 +11729,7 @@
         <v>18</v>
       </c>
       <c r="AP58" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ58" t="n">
         <v>8</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -11815,16 +11815,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G59" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="H59" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>3.25</v>
@@ -11866,7 +11866,7 @@
         <v>1.25</v>
       </c>
       <c r="W59" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="X59" t="n">
         <v>46</v>
@@ -11971,14 +11971,14 @@
         <v>1.64</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG59" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -12030,7 +12030,7 @@
         <v>1.01</v>
       </c>
       <c r="M60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N60" t="n">
         <v>5.4</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -12242,10 +12242,10 @@
         <v>1.52</v>
       </c>
       <c r="S61" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="T61" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U61" t="n">
         <v>2.32</v>
@@ -12257,22 +12257,22 @@
         <v>1.75</v>
       </c>
       <c r="X61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y61" t="n">
         <v>25</v>
       </c>
       <c r="Z61" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA61" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB61" t="n">
         <v>19</v>
       </c>
       <c r="AC61" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD61" t="n">
         <v>20</v>
@@ -12284,7 +12284,7 @@
         <v>24</v>
       </c>
       <c r="AG61" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH61" t="n">
         <v>21</v>
@@ -12293,7 +12293,7 @@
         <v>50</v>
       </c>
       <c r="AJ61" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK61" t="n">
         <v>29</v>
@@ -12311,19 +12311,19 @@
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AQ61" t="n">
         <v>13</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AT61" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AU61" t="n">
         <v>7.8</v>
@@ -12332,41 +12332,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW61" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AX61" t="n">
         <v>10.5</v>
       </c>
       <c r="AY61" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ61" t="n">
         <v>10.5</v>
       </c>
       <c r="BA61" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="BB61" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="BC61" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="BD61" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BE61" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="BF61" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="BG61" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
         <v>1.48</v>
       </c>
       <c r="S62" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="T62" t="n">
         <v>1.74</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -12621,10 +12621,10 @@
         <v>1.22</v>
       </c>
       <c r="P63" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R63" t="n">
         <v>1.54</v>
@@ -12666,7 +12666,7 @@
         <v>25</v>
       </c>
       <c r="AE63" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF63" t="n">
         <v>11.5</v>
@@ -12705,10 +12705,10 @@
         <v>21</v>
       </c>
       <c r="AR63" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS63" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT63" t="n">
         <v>8.4</v>
@@ -12732,7 +12732,7 @@
         <v>17</v>
       </c>
       <c r="BA63" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB63" t="n">
         <v>13.5</v>
@@ -12744,7 +12744,7 @@
         <v>24</v>
       </c>
       <c r="BE63" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF63" t="n">
         <v>6.2</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -12788,16 +12788,16 @@
         <v>1.56</v>
       </c>
       <c r="G64" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H64" t="n">
         <v>5.8</v>
       </c>
       <c r="I64" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K64" t="n">
         <v>4.8</v>
@@ -12812,19 +12812,19 @@
         <v>4.7</v>
       </c>
       <c r="O64" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P64" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R64" t="n">
         <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T64" t="n">
         <v>1.77</v>
@@ -12857,7 +12857,7 @@
         <v>11</v>
       </c>
       <c r="AD64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE64" t="n">
         <v>85</v>
@@ -12875,7 +12875,7 @@
         <v>85</v>
       </c>
       <c r="AJ64" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK64" t="n">
         <v>18.5</v>
@@ -12899,22 +12899,22 @@
         <v>20</v>
       </c>
       <c r="AR64" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS64" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT64" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU64" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV64" t="n">
         <v>19.5</v>
       </c>
       <c r="AW64" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX64" t="n">
         <v>9.199999999999999</v>
@@ -12935,20 +12935,20 @@
         <v>13</v>
       </c>
       <c r="BD64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE64" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF64" t="n">
         <v>5.9</v>
       </c>
       <c r="BG64" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
         <v>1.69</v>
       </c>
       <c r="G65" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H65" t="n">
         <v>4.9</v>
@@ -13030,7 +13030,7 @@
         <v>1.22</v>
       </c>
       <c r="W65" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X65" t="n">
         <v>28</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -13323,7 +13323,7 @@
         <v>9.6</v>
       </c>
       <c r="BD66" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="BE66" t="n">
         <v>10.5</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -13370,16 +13370,16 @@
         <v>1.67</v>
       </c>
       <c r="G67" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I67" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K67" t="n">
         <v>4.7</v>
@@ -13403,19 +13403,19 @@
         <v>1.69</v>
       </c>
       <c r="R67" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S67" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T67" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U67" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V67" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W67" t="n">
         <v>2.3</v>
@@ -13442,7 +13442,7 @@
         <v>22</v>
       </c>
       <c r="AE67" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF67" t="n">
         <v>12</v>
@@ -13472,19 +13472,19 @@
         <v>9</v>
       </c>
       <c r="AO67" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AP67" t="n">
         <v>17</v>
       </c>
       <c r="AQ67" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR67" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS67" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT67" t="n">
         <v>8.6</v>
@@ -13496,7 +13496,7 @@
         <v>17.5</v>
       </c>
       <c r="AW67" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX67" t="n">
         <v>10</v>
@@ -13508,7 +13508,7 @@
         <v>16</v>
       </c>
       <c r="BA67" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB67" t="n">
         <v>15</v>
@@ -13517,10 +13517,10 @@
         <v>15</v>
       </c>
       <c r="BD67" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE67" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF67" t="n">
         <v>7.6</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -13567,13 +13567,13 @@
         <v>1.58</v>
       </c>
       <c r="H68" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I68" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J68" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K68" t="n">
         <v>5.3</v>
@@ -13609,10 +13609,10 @@
         <v>2.78</v>
       </c>
       <c r="V68" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W68" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X68" t="n">
         <v>40</v>
@@ -13639,7 +13639,7 @@
         <v>60</v>
       </c>
       <c r="AF68" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG68" t="n">
         <v>10.5</v>
@@ -13660,7 +13660,7 @@
         <v>22</v>
       </c>
       <c r="AM68" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN68" t="n">
         <v>4.6</v>
@@ -13717,14 +13717,14 @@
         <v>46</v>
       </c>
       <c r="BF68" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG68" t="n">
         <v>32</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -13758,10 +13758,10 @@
         <v>2.7</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H69" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I69" t="n">
         <v>2.86</v>
@@ -13770,7 +13770,7 @@
         <v>3.55</v>
       </c>
       <c r="K69" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -13779,7 +13779,7 @@
         <v>1.05</v>
       </c>
       <c r="N69" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O69" t="n">
         <v>1.22</v>
@@ -13806,7 +13806,7 @@
         <v>1.54</v>
       </c>
       <c r="W69" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X69" t="n">
         <v>24</v>
@@ -13869,7 +13869,7 @@
         <v>14</v>
       </c>
       <c r="AR69" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS69" t="n">
         <v>36</v>
@@ -13878,22 +13878,22 @@
         <v>14</v>
       </c>
       <c r="AU69" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV69" t="n">
         <v>11.5</v>
       </c>
       <c r="AW69" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX69" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY69" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ69" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA69" t="n">
         <v>26</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G70" t="n">
         <v>2.58</v>
@@ -13991,10 +13991,10 @@
         <v>3.6</v>
       </c>
       <c r="T70" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U70" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V70" t="n">
         <v>1.45</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -14260,7 +14260,7 @@
         <v>11</v>
       </c>
       <c r="AS71" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT71" t="n">
         <v>12</v>
@@ -14275,38 +14275,38 @@
         <v>20</v>
       </c>
       <c r="AX71" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY71" t="n">
         <v>15</v>
       </c>
       <c r="AZ71" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BA71" t="n">
-        <v>36</v>
+        <v>8.4</v>
       </c>
       <c r="BB71" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE71" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC71" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BD71" t="n">
+      <c r="BF71" t="n">
         <v>9.4</v>
-      </c>
-      <c r="BE71" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF71" t="n">
-        <v>9.6</v>
       </c>
       <c r="BG71" t="n">
         <v>14</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G73" t="n">
         <v>3.95</v>
@@ -14603,7 +14603,7 @@
         <v>11</v>
       </c>
       <c r="AD73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE73" t="n">
         <v>40</v>
@@ -14639,10 +14639,10 @@
         <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AR73" t="n">
         <v>9.4</v>
@@ -14651,50 +14651,50 @@
         <v>2.02</v>
       </c>
       <c r="AT73" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AU73" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AV73" t="n">
         <v>1.88</v>
       </c>
       <c r="AW73" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AX73" t="n">
         <v>2</v>
       </c>
       <c r="AY73" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AZ73" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BA73" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BB73" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BC73" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BD73" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BE73" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BF73" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BG73" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -14749,7 +14749,7 @@
         <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>1.61</v>
+        <v>2.68</v>
       </c>
       <c r="O74" t="n">
         <v>1.38</v>
@@ -14767,10 +14767,10 @@
         <v>3.35</v>
       </c>
       <c r="T74" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U74" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V74" t="n">
         <v>1.37</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -14922,13 +14922,13 @@
         <v>2.76</v>
       </c>
       <c r="G75" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H75" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="I75" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J75" t="n">
         <v>3.45</v>
@@ -14949,16 +14949,16 @@
         <v>1.31</v>
       </c>
       <c r="P75" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R75" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S75" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="T75" t="n">
         <v>1.74</v>
@@ -14967,10 +14967,10 @@
         <v>2.1</v>
       </c>
       <c r="V75" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W75" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X75" t="n">
         <v>17</v>
@@ -14982,13 +14982,13 @@
         <v>21</v>
       </c>
       <c r="AA75" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB75" t="n">
         <v>13.5</v>
       </c>
       <c r="AC75" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD75" t="n">
         <v>14</v>
@@ -15012,10 +15012,10 @@
         <v>55</v>
       </c>
       <c r="AK75" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL75" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM75" t="n">
         <v>110</v>
@@ -15027,7 +15027,7 @@
         <v>29</v>
       </c>
       <c r="AP75" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ75" t="n">
         <v>9.4</v>
@@ -15036,19 +15036,19 @@
         <v>13.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AT75" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU75" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV75" t="n">
         <v>9.4</v>
       </c>
       <c r="AW75" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX75" t="n">
         <v>14.5</v>
@@ -15060,19 +15060,19 @@
         <v>13.5</v>
       </c>
       <c r="BA75" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BB75" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE75" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BC75" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD75" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE75" t="n">
-        <v>5</v>
       </c>
       <c r="BF75" t="n">
         <v>21</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -15113,13 +15113,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G76" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H76" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I76" t="n">
         <v>6.2</v>
@@ -15128,7 +15128,7 @@
         <v>3.1</v>
       </c>
       <c r="K76" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="L76" t="n">
         <v>1.01</v>
@@ -15137,13 +15137,13 @@
         <v>1.01</v>
       </c>
       <c r="N76" t="n">
-        <v>1.65</v>
+        <v>2.36</v>
       </c>
       <c r="O76" t="n">
         <v>1.33</v>
       </c>
       <c r="P76" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q76" t="n">
         <v>1.87</v>
@@ -15155,16 +15155,16 @@
         <v>3.1</v>
       </c>
       <c r="T76" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U76" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V76" t="n">
         <v>1.19</v>
       </c>
       <c r="W76" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X76" t="n">
         <v>1000</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15525,7 @@
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>1.81</v>
+        <v>2.76</v>
       </c>
       <c r="O78" t="n">
         <v>1.26</v>
@@ -15543,10 +15543,10 @@
         <v>2.74</v>
       </c>
       <c r="T78" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U78" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V78" t="n">
         <v>1.26</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
         <v>1.19</v>
       </c>
       <c r="P79" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q79" t="n">
         <v>1.56</v>
@@ -15746,7 +15746,7 @@
         <v>1.13</v>
       </c>
       <c r="W79" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X79" t="n">
         <v>26</v>
@@ -15767,7 +15767,7 @@
         <v>12.5</v>
       </c>
       <c r="AD79" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE79" t="n">
         <v>110</v>
@@ -15821,10 +15821,10 @@
         <v>11</v>
       </c>
       <c r="AV79" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW79" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX79" t="n">
         <v>9.199999999999999</v>
@@ -15833,7 +15833,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ79" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA79" t="n">
         <v>16</v>
@@ -15845,10 +15845,10 @@
         <v>12.5</v>
       </c>
       <c r="BD79" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BE79" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF79" t="n">
         <v>4.8</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -15922,7 +15922,7 @@
         <v>1.88</v>
       </c>
       <c r="Q80" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="R80" t="n">
         <v>1.34</v>
@@ -16018,7 +16018,7 @@
         <v>13</v>
       </c>
       <c r="AW80" t="n">
-        <v>36</v>
+        <v>9.4</v>
       </c>
       <c r="AX80" t="n">
         <v>13</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -16101,13 +16101,13 @@
         <v>6.4</v>
       </c>
       <c r="L81" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M81" t="n">
         <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="O81" t="n">
         <v>1.31</v>
@@ -16125,10 +16125,10 @@
         <v>3</v>
       </c>
       <c r="T81" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U81" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V81" t="n">
         <v>1.21</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -16501,7 +16501,7 @@
         <v>1.21</v>
       </c>
       <c r="P83" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q83" t="n">
         <v>1.59</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -16692,10 +16692,10 @@
         <v>3.35</v>
       </c>
       <c r="O84" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P84" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q84" t="n">
         <v>2.22</v>
@@ -16725,7 +16725,7 @@
         <v>9.6</v>
       </c>
       <c r="Z84" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA84" t="n">
         <v>36</v>
@@ -16749,7 +16749,7 @@
         <v>14.5</v>
       </c>
       <c r="AH84" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI84" t="n">
         <v>48</v>
@@ -16821,14 +16821,14 @@
         <v>65</v>
       </c>
       <c r="BF84" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG84" t="n">
         <v>22</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G86" t="n">
         <v>1.8</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -17295,7 +17295,7 @@
         <v>3.1</v>
       </c>
       <c r="V87" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W87" t="n">
         <v>1.69</v>
@@ -17406,11 +17406,11 @@
         <v>5.2</v>
       </c>
       <c r="BG87" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -17477,10 +17477,10 @@
         <v>1.3</v>
       </c>
       <c r="R88" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S88" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="T88" t="n">
         <v>1.37</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -17865,10 +17865,10 @@
         <v>1.87</v>
       </c>
       <c r="R90" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S90" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T90" t="n">
         <v>1.73</v>
@@ -17877,28 +17877,28 @@
         <v>2.16</v>
       </c>
       <c r="V90" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W90" t="n">
         <v>1.75</v>
       </c>
       <c r="X90" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y90" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z90" t="n">
         <v>34</v>
       </c>
       <c r="AA90" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB90" t="n">
         <v>12.5</v>
       </c>
       <c r="AC90" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD90" t="n">
         <v>18.5</v>
@@ -17907,16 +17907,16 @@
         <v>55</v>
       </c>
       <c r="AF90" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG90" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH90" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI90" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ90" t="n">
         <v>34</v>
@@ -17925,16 +17925,16 @@
         <v>28</v>
       </c>
       <c r="AL90" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM90" t="n">
         <v>110</v>
       </c>
       <c r="AN90" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO90" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP90" t="n">
         <v>13</v>
@@ -17946,10 +17946,10 @@
         <v>19.5</v>
       </c>
       <c r="AS90" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AT90" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU90" t="n">
         <v>7</v>
@@ -17958,41 +17958,41 @@
         <v>11</v>
       </c>
       <c r="AW90" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="AX90" t="n">
         <v>10.5</v>
       </c>
       <c r="AY90" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ90" t="n">
         <v>14.5</v>
       </c>
       <c r="BA90" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="BB90" t="n">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC90" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BD90" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE90" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BF90" t="n">
         <v>11.5</v>
       </c>
       <c r="BG90" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
         <v>4.5</v>
       </c>
       <c r="H91" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I91" t="n">
         <v>2.4</v>
@@ -18047,7 +18047,7 @@
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O91" t="n">
         <v>1.36</v>
@@ -18056,7 +18056,7 @@
         <v>1.72</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R91" t="n">
         <v>1.23</v>
@@ -18065,10 +18065,10 @@
         <v>3.35</v>
       </c>
       <c r="T91" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U91" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V91" t="n">
         <v>1.01</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -18220,34 +18220,34 @@
         <v>1.04</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="H92" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I92" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J92" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K92" t="n">
         <v>950</v>
       </c>
       <c r="L92" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M92" t="n">
         <v>1.01</v>
       </c>
       <c r="N92" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="O92" t="n">
         <v>1.14</v>
       </c>
       <c r="P92" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q92" t="n">
         <v>1.14</v>
@@ -18256,19 +18256,19 @@
         <v>1.29</v>
       </c>
       <c r="S92" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T92" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U92" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V92" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="W92" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="X92" t="n">
         <v>1000</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
         <v>3.4</v>
       </c>
       <c r="I93" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="J93" t="n">
         <v>2.96</v>
@@ -18435,31 +18435,31 @@
         <v>1.01</v>
       </c>
       <c r="N93" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="O93" t="n">
         <v>1.3</v>
       </c>
       <c r="P93" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="R93" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S93" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T93" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V93" t="n">
         <v>1.18</v>
-      </c>
-      <c r="S93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T93" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U93" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V93" t="n">
-        <v>1.1</v>
       </c>
       <c r="W93" t="n">
         <v>1.75</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-05-06 21:20:12</t>
+          <t>2026-05-06 23:36:18</t>
         </is>
       </c>
     </row>
